--- a/branches/restrict-interpretation-vs/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
+++ b/branches/restrict-interpretation-vs/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T10:24:05+00:00</t>
+    <t>2026-09-01T07:36:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/restrict-interpretation-vs/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
+++ b/branches/restrict-interpretation-vs/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T07:36:06+00:00</t>
+    <t>2026-09-01T07:48:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/restrict-interpretation-vs/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
+++ b/branches/restrict-interpretation-vs/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T07:48:18+00:00</t>
+    <t>2026-09-01T07:55:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2075,7 +2075,7 @@
     <t>For some results, particularly numeric results, an interpretation is necessary to fully understand the significance of a result.</t>
   </si>
   <si>
-    <t>Eingeschränkte Auswahl aus HL7 v3 ObservationInterpretation. Lokal gebräuchliche Skalen wie -- - N + ++ bzw. L N H bilden auf diese Konzepte ab. Die Bindung ist extensible: für Werte jenseits der Telefongrenze können zusätzlich die abnormal-Codes HH, LL und AA verwendet werden.</t>
+    <t>Eingeschränkte Auswahl aus HL7 v3 ObservationInterpretation. Lokale Kodierungen wie -- - N + ++ oder L N H lassen sich auf diese Konzepte abbilden. Die Bindung ist extensible: zum Beispiel für Werte jenseits der Telefongrenze können aus dem v3-ObservationInterpretation ValueSet zusätzlich die abnormal-Codes HH, LL und AA verwendet werden.</t>
   </si>
   <si>
     <t>https://www.medizininformatik-initiative.de/fhir/core/modul-labor/ValueSet/Interpretation</t>
@@ -2915,7 +2915,7 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="227.5078125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="255.0" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="86.3984375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>

--- a/branches/restrict-interpretation-vs/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
+++ b/branches/restrict-interpretation-vs/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T07:55:52+00:00</t>
+    <t>2026-09-01T08:05:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2075,7 +2075,7 @@
     <t>For some results, particularly numeric results, an interpretation is necessary to fully understand the significance of a result.</t>
   </si>
   <si>
-    <t>Eingeschränkte Auswahl aus HL7 v3 ObservationInterpretation. Lokale Kodierungen wie -- - N + ++ oder L N H lassen sich auf diese Konzepte abbilden. Die Bindung ist extensible: zum Beispiel für Werte jenseits der Telefongrenze können aus dem v3-ObservationInterpretation ValueSet zusätzlich die abnormal-Codes HH, LL und AA verwendet werden.</t>
+    <t>Eingeschränkte Auswahl aus HL7 v3 ObservationInterpretation. FHIR bindet dieses Element extensible an das vollstaendige ValueSet Observation Interpretation Codes; das Modul schraenkt auf die im Laborkontext sinnvollen Konzepte ein. Lokale Kodierungen wie -- - N + ++ oder L N H lassen sich darauf abbilden. Da die Bindung extensible bleibt, sind zum Beispiel fuer Werte jenseits der Telefongrenze zusaetzlich die abnormal-Codes HH, LL und AA zulaessig.</t>
   </si>
   <si>
     <t>https://www.medizininformatik-initiative.de/fhir/core/modul-labor/ValueSet/Interpretation</t>

--- a/branches/restrict-interpretation-vs/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
+++ b/branches/restrict-interpretation-vs/StructureDefinition-mii-pr-labor-laboruntersuchung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T08:05:25+00:00</t>
+    <t>2026-09-01T08:13:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2075,7 +2075,7 @@
     <t>For some results, particularly numeric results, an interpretation is necessary to fully understand the significance of a result.</t>
   </si>
   <si>
-    <t>Eingeschränkte Auswahl aus HL7 v3 ObservationInterpretation. FHIR bindet dieses Element extensible an das vollstaendige ValueSet Observation Interpretation Codes; das Modul schraenkt auf die im Laborkontext sinnvollen Konzepte ein. Lokale Kodierungen wie -- - N + ++ oder L N H lassen sich darauf abbilden. Da die Bindung extensible bleibt, sind zum Beispiel fuer Werte jenseits der Telefongrenze zusaetzlich die abnormal-Codes HH, LL und AA zulaessig.</t>
+    <t>Eingeschränkte Auswahl aus HL7 v3 ObservationInterpretation. FHIR bindet dieses Element extensible an das vollständige ValueSet Observation Interpretation Codes; das Modul schränkt auf die im Laborkontext sinnvollen Konzepte ein. Lokale Kodierungen wie -- - N + ++ oder L N H lassen sich darauf abbilden. Da die Bindung extensible ist, dürfen darüber hinaus weitere Codes verwendet werden; praktisch relevant sind die abnormal-Codes HH, LL und AA, etwa für Werte jenseits der Telefongrenze.</t>
   </si>
   <si>
     <t>https://www.medizininformatik-initiative.de/fhir/core/modul-labor/ValueSet/Interpretation</t>
